--- a/Raw Data/two forces (15 trials)(tapered and cylindrical)/Validation(1.75)(3tendon).xlsx
+++ b/Raw Data/two forces (15 trials)(tapered and cylindrical)/Validation(1.75)(3tendon).xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/SoRoSim Robots/my_robot(1.75)(3tendon)/10-08-2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/two forces (15 trials)(tapered and cylindrical)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2720" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C45774B7-CACB-4184-AB66-71EC2E0943BB}"/>
+  <xr:revisionPtr revIDLastSave="2721" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E44435A-9744-4AB2-88E0-882DF511DFE5}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation (double)" sheetId="12" r:id="rId1"/>
     <sheet name="Distal Validati (double)" sheetId="19" r:id="rId2"/>
-    <sheet name="Distal Vali (opposite 15 trial)" sheetId="28" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="26" r:id="rId4"/>
-    <sheet name="Conversion" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="29" r:id="rId3"/>
+    <sheet name="Distal Vali (opposite 15 trial)" sheetId="28" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="26" r:id="rId5"/>
+    <sheet name="Conversion" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -495,6 +496,8 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -546,8 +549,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -904,68 +905,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B763EDC-8536-442D-A8D3-F37978D4DE80}">
   <dimension ref="A1:AC18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="7.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="20" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="22" t="s">
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="24" t="s">
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="25"/>
-      <c r="AC1" s="26"/>
-    </row>
-    <row r="2" spans="1:29" ht="16" x14ac:dyDescent="0.4">
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="27"/>
+      <c r="AC1" s="28"/>
+    </row>
+    <row r="2" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -1054,7 +1055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>0.3</v>
       </c>
@@ -1115,7 +1116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>0.4</v>
       </c>
@@ -1212,7 +1213,7 @@
         <v>2.2138105950477785E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>0.7</v>
       </c>
@@ -1309,7 +1310,7 @@
         <v>-9.3957033574980434E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>0.7</v>
       </c>
@@ -1406,7 +1407,7 @@
         <v>-0.1356491294248488</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>0.6</v>
       </c>
@@ -1503,7 +1504,7 @@
         <v>5.8335136445672675E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>0.8</v>
       </c>
@@ -1600,7 +1601,7 @@
         <v>8.3703172439121926E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>0.3</v>
       </c>
@@ -1697,7 +1698,7 @@
         <v>2.8620525882628089E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>0.5</v>
       </c>
@@ -1794,7 +1795,7 @@
         <v>8.2357309889192765E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>0.4</v>
       </c>
@@ -1891,7 +1892,7 @@
         <v>5.3695500075776781E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>0.7</v>
       </c>
@@ -1988,7 +1989,7 @@
         <v>0.16824601495003511</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>0.3</v>
       </c>
@@ -2085,7 +2086,7 @@
         <v>0.14363298813659309</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>0.6</v>
       </c>
@@ -2182,7 +2183,7 @@
         <v>5.652327756871145E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>0.7</v>
       </c>
@@ -2279,7 +2280,7 @@
         <v>-6.4146645615533626E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>0.4</v>
       </c>
@@ -2376,7 +2377,7 @@
         <v>0.14065421166017467</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>0.8</v>
       </c>
@@ -2473,7 +2474,7 @@
         <v>0.15293837382443365</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="X18" s="17"/>
       <c r="Y18" s="17"/>
       <c r="Z18" s="17"/>
@@ -2497,101 +2498,101 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309BE333-3BAE-4E8D-AF02-67A9E2013036}">
   <dimension ref="A1:AS17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7265625" customWidth="1"/>
-    <col min="27" max="27" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" customWidth="1"/>
+    <col min="27" max="27" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="11" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="20" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="30" t="s">
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="31"/>
-      <c r="Z1" s="31"/>
-      <c r="AA1" s="28" t="s">
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
-      <c r="AH1" s="28"/>
-      <c r="AI1" s="29" t="s">
+      <c r="AB1" s="30"/>
+      <c r="AC1" s="30"/>
+      <c r="AD1" s="30"/>
+      <c r="AE1" s="30"/>
+      <c r="AF1" s="30"/>
+      <c r="AG1" s="30"/>
+      <c r="AH1" s="30"/>
+      <c r="AI1" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="29"/>
-      <c r="AK1" s="29"/>
-      <c r="AL1" s="29"/>
-      <c r="AM1" s="29"/>
-      <c r="AN1" s="29"/>
-      <c r="AO1" s="29"/>
-      <c r="AP1" s="29"/>
-      <c r="AQ1" s="29"/>
-      <c r="AR1" s="29"/>
-      <c r="AS1" s="29"/>
-    </row>
-    <row r="2" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AJ1" s="31"/>
+      <c r="AK1" s="31"/>
+      <c r="AL1" s="31"/>
+      <c r="AM1" s="31"/>
+      <c r="AN1" s="31"/>
+      <c r="AO1" s="31"/>
+      <c r="AP1" s="31"/>
+      <c r="AQ1" s="31"/>
+      <c r="AR1" s="31"/>
+      <c r="AS1" s="31"/>
+    </row>
+    <row r="2" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -2703,18 +2704,18 @@
       <c r="AK2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="AL2" s="27" t="s">
+      <c r="AL2" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="AM2" s="27"/>
-      <c r="AN2" s="27"/>
-      <c r="AO2" s="27"/>
-      <c r="AP2" s="27"/>
-      <c r="AQ2" s="27"/>
-      <c r="AR2" s="27"/>
-      <c r="AS2" s="27"/>
-    </row>
-    <row r="3" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AM2" s="29"/>
+      <c r="AN2" s="29"/>
+      <c r="AO2" s="29"/>
+      <c r="AP2" s="29"/>
+      <c r="AQ2" s="29"/>
+      <c r="AR2" s="29"/>
+      <c r="AS2" s="29"/>
+    </row>
+    <row r="3" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>'Proximal Validation (double)'!A3</f>
         <v>0.3</v>
@@ -2861,7 +2862,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <f>'Proximal Validation (double)'!A4</f>
         <v>0.4</v>
@@ -3034,7 +3035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>'Proximal Validation (double)'!A5</f>
         <v>0.7</v>
@@ -3174,18 +3175,18 @@
         <f t="shared" si="8"/>
         <v>3.3854009683146336E-3</v>
       </c>
-      <c r="AL5" s="27" t="s">
+      <c r="AL5" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="AM5" s="27"/>
-      <c r="AN5" s="27"/>
-      <c r="AO5" s="27"/>
-      <c r="AP5" s="27"/>
-      <c r="AQ5" s="27"/>
-      <c r="AR5" s="27"/>
-      <c r="AS5" s="27"/>
-    </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="AM5" s="29"/>
+      <c r="AN5" s="29"/>
+      <c r="AO5" s="29"/>
+      <c r="AP5" s="29"/>
+      <c r="AQ5" s="29"/>
+      <c r="AR5" s="29"/>
+      <c r="AS5" s="29"/>
+    </row>
+    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>'Proximal Validation (double)'!A6</f>
         <v>0.7</v>
@@ -3340,7 +3341,7 @@
       <c r="AR6" s="8"/>
       <c r="AS6" s="8"/>
     </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>'Proximal Validation (double)'!A7</f>
         <v>0.6</v>
@@ -3498,7 +3499,7 @@
       <c r="AR7" s="8"/>
       <c r="AS7" s="8"/>
     </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>'Proximal Validation (double)'!A8</f>
         <v>0.8</v>
@@ -3639,7 +3640,7 @@
         <v>0.48035321567774947</v>
       </c>
     </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>'Proximal Validation (double)'!A9</f>
         <v>0.3</v>
@@ -3783,7 +3784,7 @@
       <c r="AM9" s="13"/>
       <c r="AN9" s="13"/>
     </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>'Proximal Validation (double)'!A10</f>
         <v>0.5</v>
@@ -3924,7 +3925,7 @@
         <v>2.9369850030887434E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>'Proximal Validation (double)'!A11</f>
         <v>0.4</v>
@@ -4068,7 +4069,7 @@
       <c r="AM11" s="13"/>
       <c r="AN11" s="13"/>
     </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f>'Proximal Validation (double)'!A12</f>
         <v>0.7</v>
@@ -4209,7 +4210,7 @@
         <v>0.15731858483240013</v>
       </c>
     </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <f>'Proximal Validation (double)'!A13</f>
         <v>0.3</v>
@@ -4353,7 +4354,7 @@
       <c r="AM13" s="13"/>
       <c r="AN13" s="13"/>
     </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f>'Proximal Validation (double)'!A14</f>
         <v>0.6</v>
@@ -4494,7 +4495,7 @@
         <v>0.10819024237208952</v>
       </c>
     </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <f>'Proximal Validation (double)'!A15</f>
         <v>0.7</v>
@@ -4635,7 +4636,7 @@
         <v>0.35197190214422736</v>
       </c>
     </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <f>'Proximal Validation (double)'!A16</f>
         <v>0.4</v>
@@ -4776,7 +4777,7 @@
         <v>0.17578353094574961</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f>'Proximal Validation (double)'!A17</f>
         <v>0.8</v>
@@ -4933,103 +4934,112 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32023CAE-8074-4E42-A323-4CB20D272436}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED6ED5A-CA70-46B7-8B78-D4A73042C32F}">
   <dimension ref="A1:AS17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="11" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="20" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="30" t="s">
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="31"/>
-      <c r="Z1" s="31"/>
-      <c r="AA1" s="28" t="s">
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
-      <c r="AH1" s="28"/>
-      <c r="AI1" s="29" t="s">
+      <c r="AB1" s="30"/>
+      <c r="AC1" s="30"/>
+      <c r="AD1" s="30"/>
+      <c r="AE1" s="30"/>
+      <c r="AF1" s="30"/>
+      <c r="AG1" s="30"/>
+      <c r="AH1" s="30"/>
+      <c r="AI1" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="29"/>
-      <c r="AK1" s="29"/>
-      <c r="AL1" s="29"/>
-      <c r="AM1" s="29"/>
-      <c r="AN1" s="29"/>
-      <c r="AO1" s="29"/>
-      <c r="AP1" s="29"/>
-      <c r="AQ1" s="29"/>
-      <c r="AR1" s="29"/>
-      <c r="AS1" s="29"/>
-    </row>
-    <row r="2" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AJ1" s="31"/>
+      <c r="AK1" s="31"/>
+      <c r="AL1" s="31"/>
+      <c r="AM1" s="31"/>
+      <c r="AN1" s="31"/>
+      <c r="AO1" s="31"/>
+      <c r="AP1" s="31"/>
+      <c r="AQ1" s="31"/>
+      <c r="AR1" s="31"/>
+      <c r="AS1" s="31"/>
+    </row>
+    <row r="2" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -5141,18 +5151,18 @@
       <c r="AK2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="AL2" s="27" t="s">
+      <c r="AL2" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="AM2" s="27"/>
-      <c r="AN2" s="27"/>
-      <c r="AO2" s="27"/>
-      <c r="AP2" s="27"/>
-      <c r="AQ2" s="27"/>
-      <c r="AR2" s="27"/>
-      <c r="AS2" s="27"/>
-    </row>
-    <row r="3" spans="1:45" ht="16" x14ac:dyDescent="0.4">
+      <c r="AM2" s="29"/>
+      <c r="AN2" s="29"/>
+      <c r="AO2" s="29"/>
+      <c r="AP2" s="29"/>
+      <c r="AQ2" s="29"/>
+      <c r="AR2" s="29"/>
+      <c r="AS2" s="29"/>
+    </row>
+    <row r="3" spans="1:45" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>0.7</v>
       </c>
@@ -5231,7 +5241,7 @@
       <c r="Y3" s="14">
         <v>1.5707963267948966</v>
       </c>
-      <c r="Z3" s="35">
+      <c r="Z3" s="18">
         <v>3.1459483137183043E-8</v>
       </c>
       <c r="AA3" s="14">
@@ -5267,15 +5277,15 @@
         <v>0</v>
       </c>
       <c r="AI3" s="16">
-        <f>AVERAGE(ABS(AA3),ABS(AE3))</f>
+        <f t="shared" ref="AI3:AK6" si="1">AVERAGE(ABS(AA3),ABS(AE3))</f>
         <v>0.10467620287260729</v>
       </c>
       <c r="AJ3" s="16">
-        <f>AVERAGE(ABS(AB3),ABS(AF3))</f>
+        <f t="shared" si="1"/>
         <v>3.9941959389010018E-2</v>
       </c>
       <c r="AK3" s="16">
-        <f>AVERAGE(ABS(AC3),ABS(AG3))</f>
+        <f t="shared" si="1"/>
         <v>3.9872703225207751E-4</v>
       </c>
       <c r="AL3" s="1" t="s">
@@ -5303,7 +5313,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>0.7</v>
       </c>
@@ -5314,7 +5324,7 @@
         <v>1.57</v>
       </c>
       <c r="D4" s="5">
-        <f t="shared" ref="D4:D17" si="1">PI()/2</f>
+        <f t="shared" ref="D4:D17" si="2">PI()/2</f>
         <v>1.5707963267948966</v>
       </c>
       <c r="E4" s="5">
@@ -5324,11 +5334,11 @@
         <v>0.06</v>
       </c>
       <c r="G4" s="5">
-        <f t="shared" ref="G4:G10" si="2">3*PI()/2</f>
+        <f t="shared" ref="G4:G10" si="3">3*PI()/2</f>
         <v>4.7123889803846897</v>
       </c>
       <c r="H4" s="5">
-        <f t="shared" ref="H4:H17" si="3">PI()/2</f>
+        <f t="shared" ref="H4:H17" si="4">PI()/2</f>
         <v>1.5707963267948966</v>
       </c>
       <c r="I4" s="5">
@@ -5382,51 +5392,51 @@
       <c r="Y4" s="5">
         <v>1.5707963267948966</v>
       </c>
-      <c r="Z4" s="36">
+      <c r="Z4" s="19">
         <v>1.7133906363022688E-7</v>
       </c>
       <c r="AA4" s="14">
-        <f t="shared" ref="AA4:AA17" si="4">R4-A4</f>
+        <f t="shared" ref="AA4:AA17" si="5">R4-A4</f>
         <v>2.0699227085119176E-4</v>
       </c>
       <c r="AB4" s="14">
-        <f t="shared" ref="AB4:AB17" si="5">S4-B4</f>
+        <f t="shared" ref="AB4:AB17" si="6">S4-B4</f>
         <v>-1.8512977295756378E-3</v>
       </c>
       <c r="AC4" s="14">
-        <f t="shared" ref="AC4:AC17" si="6">T4-C4</f>
+        <f t="shared" ref="AC4:AC17" si="7">T4-C4</f>
         <v>7.9453381991489991E-4</v>
       </c>
       <c r="AD4" s="14">
-        <f t="shared" ref="AD4:AD17" si="7">U4-D4</f>
+        <f t="shared" ref="AD4:AD17" si="8">U4-D4</f>
         <v>0</v>
       </c>
       <c r="AE4" s="14">
-        <f t="shared" ref="AE4:AE17" si="8">V4-E4</f>
+        <f t="shared" ref="AE4:AE17" si="9">V4-E4</f>
         <v>-4.2511786962629028E-5</v>
       </c>
       <c r="AF4" s="14">
-        <f t="shared" ref="AF4:AF17" si="9">W4-F4</f>
+        <f t="shared" ref="AF4:AF17" si="10">W4-F4</f>
         <v>-4.5672406847812805E-3</v>
       </c>
       <c r="AG4" s="14">
-        <f t="shared" ref="AG4:AG17" si="10">X4-G4</f>
+        <f t="shared" ref="AG4:AG17" si="11">X4-G4</f>
         <v>-1.7929749338563283E-6</v>
       </c>
       <c r="AH4" s="14">
-        <f t="shared" ref="AH4:AH17" si="11">Y4-H4</f>
+        <f t="shared" ref="AH4:AH17" si="12">Y4-H4</f>
         <v>0</v>
       </c>
       <c r="AI4" s="9">
-        <f>AVERAGE(ABS(AA4),ABS(AE4))</f>
+        <f t="shared" si="1"/>
         <v>1.2475202890691039E-4</v>
       </c>
       <c r="AJ4" s="9">
-        <f>AVERAGE(ABS(AB4),ABS(AF4))</f>
+        <f t="shared" si="1"/>
         <v>3.2092692071784591E-3</v>
       </c>
       <c r="AK4" s="9">
-        <f>AVERAGE(ABS(AC4),ABS(AG4))</f>
+        <f t="shared" si="1"/>
         <v>3.9816339742437812E-4</v>
       </c>
       <c r="AL4" s="8" cm="1">
@@ -5462,7 +5472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>0.5</v>
       </c>
@@ -5473,7 +5483,7 @@
         <v>1.57</v>
       </c>
       <c r="D5" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="E5" s="5">
@@ -5483,11 +5493,11 @@
         <v>0.08</v>
       </c>
       <c r="G5" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.7123889803846897</v>
       </c>
       <c r="H5" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="I5" s="5">
@@ -5541,65 +5551,65 @@
       <c r="Y5" s="5">
         <v>1.5707963267948966</v>
       </c>
-      <c r="Z5" s="36">
+      <c r="Z5" s="19">
         <v>8.9180637323764055E-10</v>
       </c>
       <c r="AA5" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-9.5179799249433261E-2</v>
       </c>
       <c r="AB5" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.3465911166395421E-2</v>
       </c>
       <c r="AC5" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.9597711711332231E-4</v>
       </c>
       <c r="AD5" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE5" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-9.5133439835290767E-2</v>
       </c>
       <c r="AF5" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.7486025115475016E-2</v>
       </c>
       <c r="AG5" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-3.4967780138117632E-7</v>
       </c>
       <c r="AH5" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AI5" s="9">
-        <f>AVERAGE(ABS(AA5),ABS(AE5))</f>
+        <f t="shared" si="1"/>
         <v>9.5156619542362014E-2</v>
       </c>
       <c r="AJ5" s="9">
-        <f>AVERAGE(ABS(AB5),ABS(AF5))</f>
+        <f t="shared" si="1"/>
         <v>3.5475968140935218E-2</v>
       </c>
       <c r="AK5" s="9">
-        <f>AVERAGE(ABS(AC5),ABS(AG5))</f>
+        <f t="shared" si="1"/>
         <v>3.9816339745735174E-4</v>
       </c>
-      <c r="AL5" s="27" t="s">
+      <c r="AL5" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="AM5" s="27"/>
-      <c r="AN5" s="27"/>
-      <c r="AO5" s="27"/>
-      <c r="AP5" s="27"/>
-      <c r="AQ5" s="27"/>
-      <c r="AR5" s="27"/>
-      <c r="AS5" s="27"/>
-    </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="AM5" s="29"/>
+      <c r="AN5" s="29"/>
+      <c r="AO5" s="29"/>
+      <c r="AP5" s="29"/>
+      <c r="AQ5" s="29"/>
+      <c r="AR5" s="29"/>
+      <c r="AS5" s="29"/>
+    </row>
+    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>0.4</v>
       </c>
@@ -5610,7 +5620,7 @@
         <v>1.57</v>
       </c>
       <c r="D6" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="E6" s="5">
@@ -5620,11 +5630,11 @@
         <v>0.04</v>
       </c>
       <c r="G6" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.7123889803846897</v>
       </c>
       <c r="H6" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="I6" s="5">
@@ -5678,51 +5688,51 @@
       <c r="Y6" s="5">
         <v>1.5707963267948966</v>
       </c>
-      <c r="Z6" s="36">
+      <c r="Z6" s="19">
         <v>3.4805595064926673E-9</v>
       </c>
       <c r="AA6" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.2635833004832082E-3</v>
       </c>
       <c r="AB6" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.1875874993470481E-2</v>
       </c>
       <c r="AC6" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.9621008981267671E-4</v>
       </c>
       <c r="AD6" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE6" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.7875599156665922E-3</v>
       </c>
       <c r="AF6" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.8939233077990802E-3</v>
       </c>
       <c r="AG6" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.1670508381911304E-7</v>
       </c>
       <c r="AH6" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AI6" s="9">
-        <f>AVERAGE(ABS(AA6),ABS(AE6))</f>
+        <f t="shared" si="1"/>
         <v>2.5255716080749002E-3</v>
       </c>
       <c r="AJ6" s="9">
-        <f>AVERAGE(ABS(AB6),ABS(AF6))</f>
+        <f t="shared" si="1"/>
         <v>8.8848991506347806E-3</v>
       </c>
       <c r="AK6" s="9">
-        <f>AVERAGE(ABS(AC6),ABS(AG6))</f>
+        <f t="shared" si="1"/>
         <v>3.9816339744824791E-4</v>
       </c>
       <c r="AL6" s="7" t="s">
@@ -5740,7 +5750,7 @@
       <c r="AR6" s="8"/>
       <c r="AS6" s="8"/>
     </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>0.6</v>
       </c>
@@ -5751,7 +5761,7 @@
         <v>1.57</v>
       </c>
       <c r="D7" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="E7" s="5">
@@ -5761,11 +5771,11 @@
         <v>0.02</v>
       </c>
       <c r="G7" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.7123889803846897</v>
       </c>
       <c r="H7" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="I7" s="5">
@@ -5819,51 +5829,51 @@
       <c r="Y7" s="5">
         <v>1.5707963267948966</v>
       </c>
-      <c r="Z7" s="36">
+      <c r="Z7" s="19">
         <v>2.2093317019843322E-8</v>
       </c>
       <c r="AA7" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.4893658549103024E-2</v>
       </c>
       <c r="AB7" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.2853628426167302E-2</v>
       </c>
       <c r="AC7" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.9416380558039457E-4</v>
       </c>
       <c r="AD7" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE7" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6.2481002587220336E-2</v>
       </c>
       <c r="AF7" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.5575975441385072E-2</v>
       </c>
       <c r="AG7" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-2.1629892712482501E-6</v>
       </c>
       <c r="AH7" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AI7" s="16">
-        <f t="shared" ref="AI7:AI17" si="12">AVERAGE(ABS(AA7),ABS(AE7))</f>
+        <f t="shared" ref="AI7:AI17" si="13">AVERAGE(ABS(AA7),ABS(AE7))</f>
         <v>7.368733056816168E-2</v>
       </c>
       <c r="AJ7" s="16">
-        <f t="shared" ref="AJ7:AJ17" si="13">AVERAGE(ABS(AB7),ABS(AF7))</f>
+        <f t="shared" ref="AJ7:AJ17" si="14">AVERAGE(ABS(AB7),ABS(AF7))</f>
         <v>1.9214801933776185E-2</v>
       </c>
       <c r="AK7" s="16">
-        <f t="shared" ref="AK7:AK17" si="14">AVERAGE(ABS(AC7),ABS(AG7))</f>
+        <f t="shared" ref="AK7:AK17" si="15">AVERAGE(ABS(AC7),ABS(AG7))</f>
         <v>3.9816339742582141E-4</v>
       </c>
       <c r="AL7" s="11">
@@ -5871,11 +5881,11 @@
         <v>8.1676126569716123E-2</v>
       </c>
       <c r="AM7" s="11">
-        <f t="shared" ref="AM7:AN7" si="15">AVERAGE(AM4,AQ4)</f>
+        <f t="shared" ref="AM7:AN7" si="16">AVERAGE(AM4,AQ4)</f>
         <v>2.2700956745989969E-2</v>
       </c>
       <c r="AN7" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.0393706459515003E-4</v>
       </c>
       <c r="AO7" s="8"/>
@@ -5884,7 +5894,7 @@
       <c r="AR7" s="8"/>
       <c r="AS7" s="8"/>
     </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>0.8</v>
       </c>
@@ -5895,7 +5905,7 @@
         <v>1.57</v>
       </c>
       <c r="D8" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="E8" s="5">
@@ -5905,11 +5915,11 @@
         <v>0.06</v>
       </c>
       <c r="G8" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.7123889803846897</v>
       </c>
       <c r="H8" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="I8" s="5">
@@ -5963,55 +5973,55 @@
       <c r="Y8" s="5">
         <v>1.5707963267948966</v>
       </c>
-      <c r="Z8" s="36">
+      <c r="Z8" s="19">
         <v>2.8699779326886478E-7</v>
       </c>
       <c r="AA8" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-6.9540714384616398E-2</v>
       </c>
       <c r="AB8" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-2.6177918602618699E-3</v>
       </c>
       <c r="AC8" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.9419882510234352E-4</v>
       </c>
       <c r="AD8" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE8" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-5.9543954870906912E-2</v>
       </c>
       <c r="AF8" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-1.5936335225440509E-2</v>
       </c>
       <c r="AG8" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-2.1279698190213026E-6</v>
       </c>
       <c r="AH8" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AI8" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.4542334627761655E-2</v>
       </c>
       <c r="AJ8" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.2770635428511897E-3</v>
       </c>
       <c r="AK8" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3.9816339746068241E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>0.3</v>
       </c>
@@ -6022,7 +6032,7 @@
         <v>1.57</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="E9" s="5">
@@ -6032,11 +6042,11 @@
         <v>0.08</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.7123889803846897</v>
       </c>
       <c r="H9" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="I9" s="5">
@@ -6090,55 +6100,55 @@
       <c r="Y9" s="5">
         <v>1.5707963267948966</v>
       </c>
-      <c r="Z9" s="36">
+      <c r="Z9" s="19">
         <v>1.141412502609362E-9</v>
       </c>
       <c r="AA9" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.14437441002279056</v>
       </c>
       <c r="AB9" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-4.7326945820858113E-2</v>
       </c>
       <c r="AC9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.8599096788489753E-4</v>
       </c>
       <c r="AD9" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE9" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.14521398256984086</v>
       </c>
       <c r="AF9" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-1.2798405197355284E-2</v>
       </c>
       <c r="AG9" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.0335826969409823E-5</v>
       </c>
       <c r="AH9" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AI9" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.14479419629631571</v>
       </c>
       <c r="AJ9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.0062675509106698E-2</v>
       </c>
       <c r="AK9" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3.9816339742715368E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>0.4</v>
       </c>
@@ -6149,7 +6159,7 @@
         <v>1.57</v>
       </c>
       <c r="D10" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="E10" s="5">
@@ -6159,11 +6169,11 @@
         <v>0.04</v>
       </c>
       <c r="G10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.7123889803846897</v>
       </c>
       <c r="H10" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="I10" s="5">
@@ -6217,55 +6227,55 @@
       <c r="Y10" s="5">
         <v>1.5707963267948966</v>
       </c>
-      <c r="Z10" s="36">
+      <c r="Z10" s="19">
         <v>5.1621818345663483E-11</v>
       </c>
       <c r="AA10" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.18775677970802152</v>
       </c>
       <c r="AB10" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-3.5817827771857019E-2</v>
       </c>
       <c r="AC10" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.9134129102276241E-4</v>
       </c>
       <c r="AD10" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE10" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.1860596622941354</v>
       </c>
       <c r="AF10" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.4167356532340872E-2</v>
       </c>
       <c r="AG10" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-4.9855039572221926E-6</v>
       </c>
       <c r="AH10" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AI10" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.18690822100107846</v>
       </c>
       <c r="AJ10" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.4992592152098946E-2</v>
       </c>
       <c r="AK10" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3.981633974899923E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>0.4</v>
       </c>
@@ -6276,7 +6286,7 @@
         <v>4.7119999999999997</v>
       </c>
       <c r="D11" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="E11" s="5">
@@ -6290,7 +6300,7 @@
         <v>1.5707963267948966</v>
       </c>
       <c r="H11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="I11" s="5">
@@ -6344,55 +6354,55 @@
       <c r="Y11" s="5">
         <v>1.5707963267948966</v>
       </c>
-      <c r="Z11" s="36">
+      <c r="Z11" s="19">
         <v>1.2717513320592856E-9</v>
       </c>
       <c r="AA11" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.2223250033888753E-2</v>
       </c>
       <c r="AB11" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.3523582399042275E-2</v>
       </c>
       <c r="AC11" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.8884441547004656E-4</v>
       </c>
       <c r="AD11" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE11" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.0678392771911192E-2</v>
       </c>
       <c r="AF11" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.4464050248331291E-2</v>
       </c>
       <c r="AG11" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.3596921877301327E-7</v>
       </c>
       <c r="AH11" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AI11" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.1450821402899972E-2</v>
       </c>
       <c r="AJ11" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.8993816323686783E-2</v>
       </c>
       <c r="AK11" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.9449019234440978E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>0.8</v>
       </c>
@@ -6403,7 +6413,7 @@
         <v>4.7119999999999997</v>
       </c>
       <c r="D12" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="E12" s="5">
@@ -6413,11 +6423,11 @@
         <v>0.02</v>
       </c>
       <c r="G12" s="5">
-        <f t="shared" ref="G12:G17" si="16">PI()/2</f>
+        <f t="shared" ref="G12:G17" si="17">PI()/2</f>
         <v>1.5707963267948966</v>
       </c>
       <c r="H12" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="I12" s="5">
@@ -6471,55 +6481,55 @@
       <c r="Y12" s="5">
         <v>1.5707963267948966</v>
       </c>
-      <c r="Z12" s="36">
+      <c r="Z12" s="19">
         <v>7.1613444830747141E-8</v>
       </c>
       <c r="AA12" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1.2007647328447946E-2</v>
       </c>
       <c r="AB12" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.0556207340696205E-2</v>
       </c>
       <c r="AC12" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.8844321494480027E-4</v>
       </c>
       <c r="AD12" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE12" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-1.8112384159698069E-2</v>
       </c>
       <c r="AF12" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.8069408589315033E-2</v>
       </c>
       <c r="AG12" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-5.3716974357520542E-7</v>
       </c>
       <c r="AH12" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AI12" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.5060015744073008E-2</v>
       </c>
       <c r="AJ12" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.4312807965005619E-2</v>
       </c>
       <c r="AK12" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.9449019234418774E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>0.3</v>
       </c>
@@ -6530,7 +6540,7 @@
         <v>4.7119999999999997</v>
       </c>
       <c r="D13" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="E13" s="5">
@@ -6540,11 +6550,11 @@
         <v>0.04</v>
       </c>
       <c r="G13" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="H13" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="I13" s="5">
@@ -6598,55 +6608,55 @@
       <c r="Y13" s="5">
         <v>1.5707963267948966</v>
       </c>
-      <c r="Z13" s="36">
+      <c r="Z13" s="19">
         <v>1.8681787595237771E-9</v>
       </c>
       <c r="AA13" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.5009156739259204E-2</v>
       </c>
       <c r="AB13" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.9765818176988359E-2</v>
       </c>
       <c r="AC13" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.8893206525347779E-4</v>
       </c>
       <c r="AD13" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE13" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.3520769588130337E-2</v>
       </c>
       <c r="AF13" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.3555128332030042E-2</v>
       </c>
       <c r="AG13" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-4.8319437118138353E-8</v>
       </c>
       <c r="AH13" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AI13" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.426496316369477E-2</v>
       </c>
       <c r="AJ13" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.66604732545092E-2</v>
       </c>
       <c r="AK13" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.9449019234529796E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>0.5</v>
       </c>
@@ -6657,7 +6667,7 @@
         <v>4.7119999999999997</v>
       </c>
       <c r="D14" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="E14" s="5">
@@ -6667,11 +6677,11 @@
         <v>0.06</v>
       </c>
       <c r="G14" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="H14" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="I14" s="5">
@@ -6725,55 +6735,55 @@
       <c r="Y14" s="5">
         <v>1.5707963267948966</v>
       </c>
-      <c r="Z14" s="36">
+      <c r="Z14" s="19">
         <v>4.0115487715714045E-9</v>
       </c>
       <c r="AA14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.5494118838661417E-2</v>
       </c>
       <c r="AB14" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1.4169102771934033E-2</v>
       </c>
       <c r="AC14" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.8710156239485372E-4</v>
       </c>
       <c r="AD14" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE14" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7.720910726719854E-2</v>
       </c>
       <c r="AF14" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-1.1178778551775639E-3</v>
       </c>
       <c r="AG14" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.8788222924115416E-6</v>
       </c>
       <c r="AH14" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AI14" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.6351613052929979E-2</v>
       </c>
       <c r="AJ14" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.6434903135557987E-3</v>
       </c>
       <c r="AK14" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.9449019234363263E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>0.4</v>
       </c>
@@ -6784,7 +6794,7 @@
         <v>4.7119999999999997</v>
       </c>
       <c r="D15" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="E15" s="5">
@@ -6794,11 +6804,11 @@
         <v>0.02</v>
       </c>
       <c r="G15" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="H15" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="I15" s="5">
@@ -6852,55 +6862,55 @@
       <c r="Y15" s="5">
         <v>1.5707963267948966</v>
       </c>
-      <c r="Z15" s="36">
+      <c r="Z15" s="19">
         <v>4.2984598364642524E-8</v>
       </c>
       <c r="AA15" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.26776081407206365</v>
       </c>
       <c r="AB15" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-4.3289800816139229E-2</v>
       </c>
       <c r="AC15" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.0073419247299569E-4</v>
       </c>
       <c r="AD15" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE15" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.26701560581716749</v>
       </c>
       <c r="AF15" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.4795410746755817E-2</v>
       </c>
       <c r="AG15" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.1753807890979573E-5</v>
       </c>
       <c r="AH15" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AI15" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.26738820994461554</v>
       </c>
       <c r="AJ15" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.4042605781447521E-2</v>
       </c>
       <c r="AK15" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.0624400018198763E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>0.7</v>
       </c>
@@ -6911,7 +6921,7 @@
         <v>4.7119999999999997</v>
       </c>
       <c r="D16" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="E16" s="5">
@@ -6921,11 +6931,11 @@
         <v>0.04</v>
       </c>
       <c r="G16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="H16" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="I16" s="5">
@@ -6979,55 +6989,55 @@
       <c r="Y16" s="5">
         <v>1.5707963267948966</v>
       </c>
-      <c r="Z16" s="36">
+      <c r="Z16" s="19">
         <v>1.1382326185054068E-7</v>
       </c>
       <c r="AA16" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.7956136265458831E-2</v>
       </c>
       <c r="AB16" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-6.3578229775257122E-3</v>
       </c>
       <c r="AC16" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.8192086528532343E-4</v>
       </c>
       <c r="AD16" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE16" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7.3320451604487857E-2</v>
       </c>
       <c r="AF16" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8.4472073377399315E-3</v>
       </c>
       <c r="AG16" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-7.0595194037181841E-6</v>
       </c>
       <c r="AH16" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AI16" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.5638293934973344E-2</v>
       </c>
       <c r="AJ16" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.4025151576328219E-3</v>
       </c>
       <c r="AK16" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.9449019234452081E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>0.7</v>
       </c>
@@ -7038,7 +7048,7 @@
         <v>4.7119999999999997</v>
       </c>
       <c r="D17" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="E17" s="5">
@@ -7048,11 +7058,11 @@
         <v>0.08</v>
       </c>
       <c r="G17" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="H17" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5707963267948966</v>
       </c>
       <c r="I17" s="5">
@@ -7106,51 +7116,51 @@
       <c r="Y17" s="5">
         <v>1.5707963267948966</v>
       </c>
-      <c r="Z17" s="36">
+      <c r="Z17" s="19">
         <v>1.9538824266773054E-8</v>
       </c>
       <c r="AA17" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-7.0613893397662109E-2</v>
       </c>
       <c r="AB17" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-2.9219581584097903E-2</v>
       </c>
       <c r="AC17" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.7904525106746689E-4</v>
       </c>
       <c r="AD17" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE17" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-3.4531612116910693E-2</v>
       </c>
       <c r="AF17" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-3.1579245152742783E-2</v>
       </c>
       <c r="AG17" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-9.9351342075504334E-6</v>
       </c>
       <c r="AH17" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AI17" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5.2572752757286401E-2</v>
       </c>
       <c r="AJ17" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.0399413368420343E-2</v>
       </c>
       <c r="AK17" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.9449019263750866E-4</v>
       </c>
     </row>
@@ -7169,12 +7179,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFC3D7D9-740E-4BB1-A5C5-EC42A3C8479B}">
   <dimension ref="A1:M36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -7218,7 +7228,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B2" s="5">
         <v>0.7</v>
       </c>
@@ -7259,7 +7269,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" s="5">
         <v>0.5</v>
       </c>
@@ -7300,7 +7310,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="5">
         <v>0.4</v>
       </c>
@@ -7341,7 +7351,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>0.6</v>
       </c>
@@ -7382,7 +7392,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
         <v>0.8</v>
       </c>
@@ -7423,7 +7433,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>0.3</v>
       </c>
@@ -7464,7 +7474,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>0.4</v>
       </c>
@@ -7505,7 +7515,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>0.4</v>
       </c>
@@ -7546,7 +7556,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>0.8</v>
       </c>
@@ -7587,7 +7597,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>0.3</v>
       </c>
@@ -7628,7 +7638,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>0.5</v>
       </c>
@@ -7669,7 +7679,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>0.4</v>
       </c>
@@ -7710,7 +7720,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>0.7</v>
       </c>
@@ -7751,7 +7761,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>0.7</v>
       </c>
@@ -7792,7 +7802,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -7827,7 +7837,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B18" s="14">
         <v>-4.8612811485079475E-14</v>
       </c>
@@ -7859,7 +7869,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B19" s="14">
         <v>1.2529336137437207E-6</v>
       </c>
@@ -7891,7 +7901,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B20" s="14">
         <v>-2.5073564491454923E-14</v>
       </c>
@@ -7923,7 +7933,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B21" s="14">
         <v>-5.242349232021524E-14</v>
       </c>
@@ -7955,7 +7965,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B22" s="14">
         <v>5.8136843028166278E-6</v>
       </c>
@@ -7987,7 +7997,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B23" s="14">
         <v>-2.7398142488234675E-14</v>
       </c>
@@ -8019,7 +8029,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B24" s="14">
         <v>-7.7963523732535485E-14</v>
       </c>
@@ -8051,7 +8061,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B25" s="14">
         <v>-1.88009326292684E-15</v>
       </c>
@@ -8083,7 +8093,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B26" s="14">
         <v>-4.0008087835757192E-14</v>
       </c>
@@ -8115,7 +8125,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B27" s="14">
         <v>-5.6285860201346709E-7</v>
       </c>
@@ -8147,7 +8157,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B28" s="14">
         <v>-1.5458756737661519E-6</v>
       </c>
@@ -8179,7 +8189,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B29" s="14">
         <v>-1.4876189780679149E-6</v>
       </c>
@@ -8211,7 +8221,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B30" s="14">
         <v>-1.5236180425602562E-13</v>
       </c>
@@ -8243,7 +8253,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B31" s="14">
         <v>-3.3588852555504678E-6</v>
       </c>
@@ -8275,7 +8285,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -8310,7 +8320,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B34" s="5">
         <v>-1.0536191985011101E-3</v>
       </c>
@@ -8342,7 +8352,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B35" s="5">
         <v>-1.71207822859287E-3</v>
       </c>
@@ -8374,7 +8384,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B36" s="5">
         <v>-7.3545798659324603E-3</v>
       </c>
@@ -8412,30 +8422,30 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048D6981-73D2-4F8C-88D7-D5FA77AC2EB0}">
   <dimension ref="A1:M18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="H1" s="32" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="H1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="34"/>
-    </row>
-    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="36"/>
+    </row>
+    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
@@ -8473,7 +8483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>-7.8237302601337405E-2</v>
       </c>
@@ -8517,7 +8527,7 @@
         <v>-7.8237302601337405E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>-0.149505704641342</v>
       </c>
@@ -8561,7 +8571,7 @@
         <v>-0.149505704641342</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0.267356157302856</v>
       </c>
@@ -8605,7 +8615,7 @@
         <v>0.267356157302856</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0.26247158646583602</v>
       </c>
@@ -8649,7 +8659,7 @@
         <v>0.26247158646583602</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0.27903902530670199</v>
       </c>
@@ -8693,7 +8703,7 @@
         <v>0.27903902530670199</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>-0.25437980890273998</v>
       </c>
@@ -8737,7 +8747,7 @@
         <v>-0.25437980890273998</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>-0.40951335430145303</v>
       </c>
@@ -8781,7 +8791,7 @@
         <v>-0.40951335430145303</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>-0.226083904504776</v>
       </c>
@@ -8825,7 +8835,7 @@
         <v>-0.226083904504776</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>-0.78116875886917103</v>
       </c>
@@ -8869,7 +8879,7 @@
         <v>-0.78116875886917103</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>-0.86582863330841098</v>
       </c>
@@ -8913,7 +8923,7 @@
         <v>-0.86582863330841098</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>-0.69461756944656405</v>
       </c>
@@ -8957,7 +8967,7 @@
         <v>-0.69461756944656405</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>-0.75469374656677202</v>
       </c>
@@ -9001,7 +9011,7 @@
         <v>-0.75469374656677202</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>-0.73054701089858998</v>
       </c>
@@ -9045,7 +9055,7 @@
         <v>-0.73054701089858998</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>-0.75926923751831099</v>
       </c>
@@ -9089,7 +9099,7 @@
         <v>-0.75926923751831099</v>
       </c>
     </row>
-    <row r="17" spans="8:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9115,7 +9125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="8:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H18">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9151,23 +9161,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E12580AD17ADB64691A1BA4C2E042DA4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6532fc6a52f3455fe895a4f720bca71c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xmlns:ns4="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9a2f75daf18a7097de825f86ff3fec6" ns3:_="" ns4:_="">
     <xsd:import namespace="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
@@ -9420,10 +9413,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65923CC5-95C4-4597-AADE-A0DCE38786F0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
+    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9446,20 +9467,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65923CC5-95C4-4597-AADE-A0DCE38786F0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
-    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Raw Data/two forces (15 trials)(tapered and cylindrical)/Validation(1.75)(3tendon).xlsx
+++ b/Raw Data/two forces (15 trials)(tapered and cylindrical)/Validation(1.75)(3tendon).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/two forces (15 trials)(tapered and cylindrical)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2721" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E44435A-9744-4AB2-88E0-882DF511DFE5}"/>
+  <xr:revisionPtr revIDLastSave="2743" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F97161C9-6368-4343-9394-82A283849136}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation (double)" sheetId="12" r:id="rId1"/>
@@ -477,7 +477,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -549,6 +549,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -904,7 +905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B763EDC-8536-442D-A8D3-F37978D4DE80}">
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
@@ -2481,6 +2482,34 @@
       <c r="AA18" s="17"/>
       <c r="AB18" s="17"/>
       <c r="AC18" s="17"/>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="X19" s="37"/>
+      <c r="Y19" s="37"/>
+      <c r="Z19" s="37"/>
+      <c r="AA19" s="37"/>
+      <c r="AB19" s="37"/>
+      <c r="AC19" s="37"/>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="X23">
+        <v>1.5832893967310925E-3</v>
+      </c>
+      <c r="Y23">
+        <v>1.2506246865850789E-2</v>
+      </c>
+      <c r="Z23">
+        <v>9.0552379506469213E-3</v>
+      </c>
+      <c r="AA23">
+        <v>5.2523176232652548E-2</v>
+      </c>
+      <c r="AB23">
+        <v>5.6390834196200265E-2</v>
+      </c>
+      <c r="AC23">
+        <v>8.1348046885126188E-2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
